--- a/site/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/headings.xlsx
+++ b/site/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Identity Source Configuration</t>
+          <t>Employee Source Configuration</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -507,7 +507,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Identity Source Configuration</t>
+          <t>Candidate Source Configuration</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -523,6 +523,182 @@
       <c r="D5" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMMWZTAACKV4TWT2F4YZRBSX</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Time-Based Provisioning Settings</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>h_01KMYRJEMS0R3QWRAXR2QCWSVS</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMYRJEMS0R3QWRAXR2QCWSVS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Time/Date Offset Configuration</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>h_01KMYRJTJJ2H29ZC28AJ9KHK15</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMYRJTJJ2H29ZC28AJ9KHK15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Attribute Settings</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>h_01KMYRN0BJNXPTRR3837ZNQYP7</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMYRN0BJNXPTRR3837ZNQYP7</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Define Employee and Candidate Integration Attributes</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>h_01KMYRNCVZG1YJWW619KQ96A18</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMYRNCVZG1YJWW619KQ96A18</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Define PII Attribute(s)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>h_01KMYRQARJB8788GMG9Y1HCAAB</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMYRQARJB8788GMG9Y1HCAAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Directory</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>h_01KMYSV9PV96AT9SYTCP204V58</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMYSV9PV96AT9SYTCP204V58</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Directory Settings</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>h_01KMYSVTCKFKEP096NJRQ1ZQ43</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMYSVTCKFKEP096NJRQ1ZQ43</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Application Configuration</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>h_01KMYSW9BB2HZ8XQWJ5B5W8PCM</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMYSW9BB2HZ8XQWJ5B5W8PCM</t>
         </is>
       </c>
     </row>

--- a/site/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/headings.xlsx
+++ b/site/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Application Configuration</t>
+          <t>Target Application Configuration</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -699,6 +699,72 @@
       <c r="D13" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMYSW9BB2HZ8XQWJ5B5W8PCM</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Synchronization Settings</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>h_01KMZ16GEBBWY8KBCPHJN8M6XB</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMZ16GEBBWY8KBCPHJN8M6XB</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Target Directory Assignment Settings</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>h_01KMZ1824CNQBF4625Q06C0571</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMZ1824CNQBF4625Q06C0571</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Employee Reactivation Settings</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_01KMZ3B5ET2RK0TNNDW7DDCXX2</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMZ3B5ET2RK0TNNDW7DDCXX2</t>
         </is>
       </c>
     </row>

--- a/site/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/headings.xlsx
+++ b/site/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -768,6 +768,50 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Manage Employee - AD</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>h_01KMZ67CMF7MZC9Z12KWZM63M2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMZ67CMF7MZC9Z12KWZM63M2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Identity Mapping</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01KMZ6J6Q96ZTPNBSK9G97VS8V</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMZ6J6Q96ZTPNBSK9G97VS8V</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/headings.xlsx
+++ b/site/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -771,7 +771,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Manage Employee - AD</t>
+          <t>Active Directory Employee Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -809,6 +809,94 @@
       <c r="D18" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMZ6J6Q96ZTPNBSK9G97VS8V</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Attribute Mapping</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01KN1N9580MCK3SYKZ8BD98XCE</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN1N9580MCK3SYKZ8BD98XCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Account Creation Settings</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01KN1BV4BD2ZYMVAQR2VCN4C5Y</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN1BV4BD2ZYMVAQR2VCN4C5Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Account Update Settings</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h_01KN1BY126ZXDV9KED1A7MR6NE</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN1BY126ZXDV9KED1A7MR6NE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Account Deactivation, Termination, and Deletion Settings</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>h_01KN1C1DZXJ7G6VVVV6WVM7QEG</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN1C1DZXJ7G6VVVV6WVM7QEG</t>
         </is>
       </c>
     </row>

--- a/site/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/headings.xlsx
+++ b/site/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -900,6 +900,138 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Active Directory Candidate Settings</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01KN1Q1DBVNKK896QB8XQXZQKD</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN1Q1DBVNKK896QB8XQXZQKD</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Identity Mapping</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_01KN2661XRCRJY62WJCK77B1E5</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN2661XRCRJY62WJCK77B1E5</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Attribute Mapping</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01KN2661XRQXJCK7SHKRGJA2NQ</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN2661XRQXJCK7SHKRGJA2NQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Account Creation Settings</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01KN2661XRH72WCZB81JT0F03C</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN2661XRH72WCZB81JT0F03C</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Account Update Settings</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01KN2661XRZY0B31E0M9N5C5D7</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN2661XRZY0B31E0M9N5C5D7</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Account Deactivation, Termination, and Deletion Settings</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01KN2661XR0M2TAV621G3Z1WKY</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN2661XR0M2TAV621G3Z1WKY</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/headings.xlsx
+++ b/site/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -463,7 +463,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Application Settings</t>
+          <t>About this Integration</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -473,41 +473,41 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>h_01KMMW0JV0V5F7YF66T7FHDKK3</t>
+          <t>h_01KN3R51HYZPMVGCRNDPV1FZXJ</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMMW0JV0V5F7YF66T7FHDKK3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN3R51HYZPMVGCRNDPV1FZXJ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Employee Source Configuration</t>
+          <t>Execution Configuration</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>h_01KMMW55HG93FK2B6THTR8281X</t>
+          <t>h_01KN3RDVRB255HRKY8QP7PMA9H</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMMW55HG93FK2B6THTR8281X</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN3RDVRB255HRKY8QP7PMA9H</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Candidate Source Configuration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -517,41 +517,41 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>h_01KMMWZTAACKV4TWT2F4YZRBSX</t>
+          <t>h_01KN3RE6HMXT8C6R5BFKH83T8S</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMMWZTAACKV4TWT2F4YZRBSX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN3RE6HMXT8C6R5BFKH83T8S</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Time-Based Provisioning Settings</t>
+          <t>Notification Centre</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>h_01KMYRJEMS0R3QWRAXR2QCWSVS</t>
+          <t>h_01KN3REBW93Z78F8HDH8K03751</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMYRJEMS0R3QWRAXR2QCWSVS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN3REBW93Z78F8HDH8K03751</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Time/Date Offset Configuration</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -561,63 +561,63 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>h_01KMYRJTJJ2H29ZC28AJ9KHK15</t>
+          <t>h_01KN3S4M9QBYR6GBV4EEC05QDX</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMYRJTJJ2H29ZC28AJ9KHK15</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN3S4M9QBYR6GBV4EEC05QDX</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Attribute Settings</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h_01KMYRN0BJNXPTRR3837ZNQYP7</t>
+          <t>h_01KN3S7P64JWV7F4RFKRKX0YK8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMYRN0BJNXPTRR3837ZNQYP7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN3S7P64JWV7F4RFKRKX0YK8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Define Employee and Candidate Integration Attributes</t>
+          <t>Application Settings</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01KMYRNCVZG1YJWW619KQ96A18</t>
+          <t>h_01KMMW0JV0V5F7YF66T7FHDKK3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMYRNCVZG1YJWW619KQ96A18</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMMW0JV0V5F7YF66T7FHDKK3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Define PII Attribute(s)</t>
+          <t>Employee Source Configuration</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -627,41 +627,41 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01KMYRQARJB8788GMG9Y1HCAAB</t>
+          <t>h_01KMMW55HG93FK2B6THTR8281X</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMYRQARJB8788GMG9Y1HCAAB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMMW55HG93FK2B6THTR8281X</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Directory</t>
+          <t>Candidate Source Configuration</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KMYSV9PV96AT9SYTCP204V58</t>
+          <t>h_01KMMWZTAACKV4TWT2F4YZRBSX</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMYSV9PV96AT9SYTCP204V58</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMMWZTAACKV4TWT2F4YZRBSX</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Directory Settings</t>
+          <t>Time-Based Provisioning Settings</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KMYSVTCKFKEP096NJRQ1ZQ43</t>
+          <t>h_01KMYRJEMS0R3QWRAXR2QCWSVS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMYSVTCKFKEP096NJRQ1ZQ43</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMYRJEMS0R3QWRAXR2QCWSVS</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Target Application Configuration</t>
+          <t>Time/Date Offset Configuration</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,41 +693,41 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KMYSW9BB2HZ8XQWJ5B5W8PCM</t>
+          <t>h_01KMYRJTJJ2H29ZC28AJ9KHK15</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMYSW9BB2HZ8XQWJ5B5W8PCM</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMYRJTJJ2H29ZC28AJ9KHK15</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Synchronization Settings</t>
+          <t>Attribute Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KMZ16GEBBWY8KBCPHJN8M6XB</t>
+          <t>h_01KMYRN0BJNXPTRR3837ZNQYP7</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMZ16GEBBWY8KBCPHJN8M6XB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMYRN0BJNXPTRR3837ZNQYP7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Target Directory Assignment Settings</t>
+          <t>Define Employee and Candidate Integration Attributes</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KMZ1824CNQBF4625Q06C0571</t>
+          <t>h_01KMYRNCVZG1YJWW619KQ96A18</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMZ1824CNQBF4625Q06C0571</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMYRNCVZG1YJWW619KQ96A18</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Employee Reactivation Settings</t>
+          <t>Define PII Attribute(s)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,63 +759,63 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KMZ3B5ET2RK0TNNDW7DDCXX2</t>
+          <t>h_01KMYRQARJB8788GMG9Y1HCAAB</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMZ3B5ET2RK0TNNDW7DDCXX2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMYRQARJB8788GMG9Y1HCAAB</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Active Directory Employee Settings</t>
+          <t>Directory</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KMZ67CMF7MZC9Z12KWZM63M2</t>
+          <t>h_01KMYSV9PV96AT9SYTCP204V58</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMZ67CMF7MZC9Z12KWZM63M2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMYSV9PV96AT9SYTCP204V58</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Identity Mapping</t>
+          <t>Directory Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KMZ6J6Q96ZTPNBSK9G97VS8V</t>
+          <t>h_01KMYSVTCKFKEP096NJRQ1ZQ43</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMZ6J6Q96ZTPNBSK9G97VS8V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMYSVTCKFKEP096NJRQ1ZQ43</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Attribute Mapping</t>
+          <t>Target Application Configuration</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,19 +825,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KN1N9580MCK3SYKZ8BD98XCE</t>
+          <t>h_01KMYSW9BB2HZ8XQWJ5B5W8PCM</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN1N9580MCK3SYKZ8BD98XCE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMYSW9BB2HZ8XQWJ5B5W8PCM</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Account Creation Settings</t>
+          <t>Synchronization Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,19 +847,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KN1BV4BD2ZYMVAQR2VCN4C5Y</t>
+          <t>h_01KMZ16GEBBWY8KBCPHJN8M6XB</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN1BV4BD2ZYMVAQR2VCN4C5Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMZ16GEBBWY8KBCPHJN8M6XB</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Account Update Settings</t>
+          <t>Target Directory Assignment Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KN1BY126ZXDV9KED1A7MR6NE</t>
+          <t>h_01KMZ1824CNQBF4625Q06C0571</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN1BY126ZXDV9KED1A7MR6NE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMZ1824CNQBF4625Q06C0571</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Account Deactivation, Termination, and Deletion Settings</t>
+          <t>Employee Reactivation Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,19 +891,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KN1C1DZXJ7G6VVVV6WVM7QEG</t>
+          <t>h_01KMZ3B5ET2RK0TNNDW7DDCXX2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN1C1DZXJ7G6VVVV6WVM7QEG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMZ3B5ET2RK0TNNDW7DDCXX2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Active Directory Candidate Settings</t>
+          <t>Active Directory Employee Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KN1Q1DBVNKK896QB8XQXZQKD</t>
+          <t>h_01KMZ67CMF7MZC9Z12KWZM63M2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN1Q1DBVNKK896QB8XQXZQKD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMZ67CMF7MZC9Z12KWZM63M2</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KN2661XRCRJY62WJCK77B1E5</t>
+          <t>h_01KMZ6J6Q96ZTPNBSK9G97VS8V</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN2661XRCRJY62WJCK77B1E5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KMZ6J6Q96ZTPNBSK9G97VS8V</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KN2661XRQXJCK7SHKRGJA2NQ</t>
+          <t>h_01KN1N9580MCK3SYKZ8BD98XCE</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN2661XRQXJCK7SHKRGJA2NQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN1N9580MCK3SYKZ8BD98XCE</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KN2661XRH72WCZB81JT0F03C</t>
+          <t>h_01KN1BV4BD2ZYMVAQR2VCN4C5Y</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN2661XRH72WCZB81JT0F03C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN1BV4BD2ZYMVAQR2VCN4C5Y</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KN2661XRZY0B31E0M9N5C5D7</t>
+          <t>h_01KN1BY126ZXDV9KED1A7MR6NE</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN2661XRZY0B31E0M9N5C5D7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN1BY126ZXDV9KED1A7MR6NE</t>
         </is>
       </c>
     </row>
@@ -1023,10 +1023,142 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>h_01KN1C1DZXJ7G6VVVV6WVM7QEG</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN1C1DZXJ7G6VVVV6WVM7QEG</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Active Directory Candidate Settings</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01KN1Q1DBVNKK896QB8XQXZQKD</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN1Q1DBVNKK896QB8XQXZQKD</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Identity Mapping</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01KN2661XRCRJY62WJCK77B1E5</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN2661XRCRJY62WJCK77B1E5</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Attribute Mapping</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01KN2661XRQXJCK7SHKRGJA2NQ</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN2661XRQXJCK7SHKRGJA2NQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Account Creation Settings</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01KN2661XRH72WCZB81JT0F03C</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN2661XRH72WCZB81JT0F03C</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Account Update Settings</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>h_01KN2661XRZY0B31E0M9N5C5D7</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN2661XRZY0B31E0M9N5C5D7</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Account Deactivation, Termination, and Deletion Settings</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
           <t>h_01KN2661XR0M2TAV621G3Z1WKY</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN2661XR0M2TAV621G3Z1WKY</t>
         </is>

--- a/site/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/headings.xlsx
+++ b/site/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1164,6 +1164,886 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Entra ID Employee Settings</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>h_01KN71MZCN8ZWS95HYN7D9HX4T</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN71MZCN8ZWS95HYN7D9HX4T</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Identity Mapping</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>h_01KN71MZCN50TRQRTK2Z61W4QV</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN71MZCN50TRQRTK2Z61W4QV</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Attribute Mapping</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>h_01KN71MZCNP7H1AKFBFKQX7CDC</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN71MZCNP7H1AKFBFKQX7CDC</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Account Creation Settings</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>h_01KN71MZCNHXTQ0C1YZ9WZ8TRA</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN71MZCNHXTQ0C1YZ9WZ8TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Account Update Settings</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>h_01KN71MZCNQ3Z6GM5QECF0VR6Y</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN71MZCNQ3Z6GM5QECF0VR6Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Account Deactivation, Termination, and Deletion Settings</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>h_01KN71MZCN41ASRJV0NQY86JNA</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN71MZCN41ASRJV0NQY86JNA</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Entra ID Candidate Settings</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>h_01KN71MZCNHNM1ZGAXZR4VPHS2</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN71MZCNHNM1ZGAXZR4VPHS2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Identity Mapping</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>h_01KN71MZCNYZ2M0XSBX3ZQBJQ7</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN71MZCNYZ2M0XSBX3ZQBJQ7</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Attribute Mapping</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>h_01KN71MZCN9SXA276PE49R9NC0</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN71MZCN9SXA276PE49R9NC0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Account Creation Settings</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>h_01KN71MZCN9HBPGQEY5F9KBGXW</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN71MZCN9HBPGQEY5F9KBGXW</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Account Update Settings</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>h_01KN71MZCNKCJZFY0PDSA1VVQG</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN71MZCNKCJZFY0PDSA1VVQG</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Account Deactivation, Termination, and Deletion Settings</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>h_01KN71MZCNZBDA080MCD49S0WQ</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN71MZCNZBDA080MCD49S0WQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Mailbox Settings</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>h_01KN6Y4G2QXCQBJS68J9QP7443</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN6Y4G2QXCQBJS68J9QP7443</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Mailbox Configuration</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>h_01KN70PM6D7X9MR27STA9VT641</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN70PM6D7X9MR27STA9VT641</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>OneDrive Settings</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>h_01KN6Y6YNZC2R0HH1K32ZNPEGH</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN6Y6YNZC2R0HH1K32ZNPEGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Device Settings</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>h_01KN6Y7RA96C8HXM2W85X86FD7</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN6Y7RA96C8HXM2W85X86FD7</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Device Configuration</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>h_01KN70QZST3XX2VM35WETCGXGT</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN70QZST3XX2VM35WETCGXGT</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Group Settings</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>h_01KN6YB969NR85AR735G8S87M4</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN6YB969NR85AR735G8S87M4</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Group Configuration</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>h_01KN70RS78F83FPECN75MC57H0</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN70RS78F83FPECN75MC57H0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Writeback Settings</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>h_01KN6YBBQTBS7EB8A618HX173P</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN6YBBQTBS7EB8A618HX173P</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Writeback Settings</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>h_01KN6YCT807DNA6RVBCRX8ZG48</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN6YCT807DNA6RVBCRX8ZG48</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>WriteBack Correlation Settings</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>h_01KN6YDCD8Y23A9WPRKZZER0N9</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN6YDCD8Y23A9WPRKZZER0N9</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>h_01KN6YEWK3ERKAQ8YNS1J7N8RC</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN6YEWK3ERKAQ8YNS1J7N8RC</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Business Groups</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>h_01KN6YFNJRZ6C2XGYPZ8T4GBWD</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN6YFNJRZ6C2XGYPZ8T4GBWD</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Define Business Groups</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>h_01KN6YFQYBDPBSF06Y31YFMW7B</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN6YFQYBDPBSF06Y31YFMW7B</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Access Rules</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>h_01KN6YJN8A6CSMMMQ04PZSAGE3</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN6YJN8A6CSMMMQ04PZSAGE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Organizational Unit (OU) Assignment Rules</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>h_01KN6YKQJD5MVN2WEDHNBTMJRB</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN6YKQJD5MVN2WEDHNBTMJRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Retention Rules</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>h_01KN6YMZR7AR9KRVQW8XCR7BM7</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN6YMZR7AR9KRVQW8XCR7BM7</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Define Retention Rules</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>h_01KN6YPJ6DYF5QVS13BTS7J8BF</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN6YPJ6DYF5QVS13BTS7J8BF</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Monitoring Rules</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>h_01KN6YNHSEERAN0KAQJ9QCVXDZ</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN6YNHSEERAN0KAQJ9QCVXDZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Monitoring Settings</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>h_01KN6YP4YZ6RJEXHQMT1G50HBZ</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN6YP4YZ6RJEXHQMT1G50HBZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Define Monitoring Rules</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>h_01KN6YQEPAK8JH9SMJSEB1ZMF0</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN6YQEPAK8JH9SMJSEB1ZMF0</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Naming Policy</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>h_01KN6YQXA814GR2BQKVTN7VESB</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN6YQXA814GR2BQKVTN7VESB</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Naming Policy Settings</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>h_01KN6YSFQHEJQ71YAVQM385TFG</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN6YSFQHEJQ71YAVQM385TFG</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Generate sAMAccountName</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>h_01KN6YSN7KA0K6CVMB09DF4086</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN6YSN7KA0K6CVMB09DF4086</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Generate UserPrincipalName (UPN)</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>h_01KN6YT6MQMSSXXADBQGAEE0WZ</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN6YT6MQMSSXXADBQGAEE0WZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Generate Email</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>h_01KN6YVAZY5P5S0ETP287HVK5M</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN6YVAZY5P5S0ETP287HVK5M</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Generate Common Name (CN)</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>h_01KN6YVYCFSTMW260K002X789B</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN6YVYCFSTMW260K002X789B</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Password Policy</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>h_01KN6YWCY6D0ADXRYKD3DY0GN1</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN6YWCY6D0ADXRYKD3DY0GN1</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Password Policy Configuration</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>h_01KN6YWPM11VSFSSER2GC2DG4T</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-AD-Entra-ID-Integration-Template-Labels/#h_01KN6YWPM11VSFSSER2GC2DG4T</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
